--- a/output/upload/S00028_1758_스마트V연금보험_무배당.xlsx
+++ b/output/upload/S00028_1758_스마트V연금보험_무배당.xlsx
@@ -725,11 +725,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -760,8 +780,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -792,8 +835,31 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00028_1758_스마트V연금보험_무배당.xlsx
+++ b/output/upload/S00028_1758_스마트V연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -889,6 +889,666 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1758233</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1758233</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1758233</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1758233</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1758233</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1758233</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1758234</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1758234</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1758234</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1758234</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1758234</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1758234</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A3:F3"/>

--- a/output/upload/S00028_1758_스마트V연금보험_무배당.xlsx
+++ b/output/upload/S00028_1758_스마트V연금보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -760,11 +760,7 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
+      <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n">
         <v>1</v>
       </c>
@@ -782,22 +778,22 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -815,13 +811,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -837,22 +828,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -870,13 +861,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -892,22 +878,22 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>1758233</t>
+          <t>1758235</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1758233</t>
+          <t>1758235</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -925,13 +911,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -947,22 +928,22 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>1758233</t>
+          <t>1758236</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1758233</t>
+          <t>1758236</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -980,13 +961,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -994,556 +970,6 @@
         </is>
       </c>
       <c r="L11" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1758233</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1758233</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>12</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
